--- a/artfynd/A 5518-2026 artfynd.xlsx
+++ b/artfynd/A 5518-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>131467712</v>
       </c>
       <c r="B2" t="n">
-        <v>91869</v>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,32 +794,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131468054</v>
+        <v>131468378</v>
       </c>
       <c r="B3" t="n">
-        <v>58073</v>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -827,24 +827,36 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lillgetmossen, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>391711</v>
+        <v>391459</v>
       </c>
       <c r="R3" t="n">
-        <v>6620037</v>
+        <v>6620097</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +888,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +898,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Fjäder</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,6 +927,253 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131468889</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Trinnmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>391963</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6620057</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Västra Ämtervik</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ca 20 stycks färsk spillning. Minst 3 sovträd nära varandra. Rapporterar dem separat.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131468054</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lillgetmossen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>391711</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6620037</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Västra Ämtervik</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
